--- a/artfynd/A 41534-2023 artfynd.xlsx
+++ b/artfynd/A 41534-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134274457</v>
       </c>
       <c r="B2" t="n">
-        <v>93293</v>
+        <v>93294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>134274453</v>
       </c>
       <c r="B3" t="n">
-        <v>93293</v>
+        <v>93294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>134274456</v>
       </c>
       <c r="B4" t="n">
-        <v>93293</v>
+        <v>93294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41534-2023 artfynd.xlsx
+++ b/artfynd/A 41534-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134274457</v>
       </c>
       <c r="B2" t="n">
-        <v>93294</v>
+        <v>93295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>134274453</v>
       </c>
       <c r="B3" t="n">
-        <v>93294</v>
+        <v>93295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>134274456</v>
       </c>
       <c r="B4" t="n">
-        <v>93294</v>
+        <v>93295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41534-2023 artfynd.xlsx
+++ b/artfynd/A 41534-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134274457</v>
       </c>
       <c r="B2" t="n">
-        <v>93295</v>
+        <v>93302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>134274453</v>
       </c>
       <c r="B3" t="n">
-        <v>93295</v>
+        <v>93302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>134274456</v>
       </c>
       <c r="B4" t="n">
-        <v>93295</v>
+        <v>93302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41534-2023 artfynd.xlsx
+++ b/artfynd/A 41534-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134274457</v>
+        <v>134274453</v>
       </c>
       <c r="B2" t="n">
-        <v>93302</v>
+        <v>93309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,26 +703,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Eriksberg, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409680</v>
+        <v>409743</v>
       </c>
       <c r="R2" t="n">
-        <v>6584415</v>
+        <v>6584430</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134274453</v>
+        <v>134274456</v>
       </c>
       <c r="B3" t="n">
-        <v>93302</v>
+        <v>93309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409743</v>
+        <v>409681</v>
       </c>
       <c r="R3" t="n">
-        <v>6584430</v>
+        <v>6584424</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -865,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -906,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134274456</v>
+        <v>134274457</v>
       </c>
       <c r="B4" t="n">
-        <v>93302</v>
+        <v>93309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,17 +925,26 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eriksberg, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409681</v>
+        <v>409680</v>
       </c>
       <c r="R4" t="n">
-        <v>6584424</v>
+        <v>6584415</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,370 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Karlstad Kommun - Eriksberg NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134274613</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Eriksberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>409695</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6584402</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Karlstad Kommun - Eriksberg NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134274451</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Eriksberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>409790</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584435</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Engla Grönvall</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Karlstad Kommun - Eriksberg NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134274459</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Eriksberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>409632</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6584429</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>

--- a/artfynd/A 41534-2023 artfynd.xlsx
+++ b/artfynd/A 41534-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134274453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134274456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134274457</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134274613</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1254,6 +1279,11 @@
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134274451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,8 +1404,21 @@
           <t>Karlstad Kommun - Eriksberg NVI 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134274459</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>